--- a/reference_templates/14_ข้อมูลสถานพัฒนาเด็กปฐมวัย_V2.xlsx
+++ b/reference_templates/14_ข้อมูลสถานพัฒนาเด็กปฐมวัย_V2.xlsx
@@ -14,6 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="14.ข้อมูลศูนย์พัฒนาเด็กเล็ก" sheetId="1" r:id="rId1"/>
+    <sheet name="14.สถานพัฒนาเด็กปฐมวัย" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -1068,4 +1069,429 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W13"/>
+  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="27" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="3"/>
+    <col min="2" max="2" width="26.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.625" style="3" customWidth="1"/>
+    <col min="5" max="6" width="8.375" style="3" customWidth="1"/>
+    <col min="7" max="14" width="9.625" style="2"/>
+    <col min="15" max="15" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="14.625" style="6" customWidth="1"/>
+    <col min="18" max="23" width="16.875" style="6" customWidth="1"/>
+    <col min="24" max="16384" width="9.625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+    </row>
+    <row r="2" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+    </row>
+    <row r="3" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="23"/>
+      <c r="B3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="21"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U3" s="13"/>
+      <c r="V3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="W3" s="12"/>
+    </row>
+    <row r="4" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="23"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="21"/>
+      <c r="P4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+    </row>
+    <row r="8" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+    </row>
+    <row r="9" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+    </row>
+    <row r="10" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+    </row>
+    <row r="13" spans="1:23" ht="24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="G2:N2"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>